--- a/artfynd/A 29487-2024 artfynd.xlsx
+++ b/artfynd/A 29487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028219</v>
       </c>
       <c r="B2" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127026790</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127027191</v>
       </c>
       <c r="B4" t="n">
-        <v>80084</v>
+        <v>80115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127028208</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127027248</v>
       </c>
       <c r="B6" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29487-2024 artfynd.xlsx
+++ b/artfynd/A 29487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028219</v>
       </c>
       <c r="B2" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127026790</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127027191</v>
       </c>
       <c r="B4" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127028208</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127027248</v>
       </c>
       <c r="B6" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29487-2024 artfynd.xlsx
+++ b/artfynd/A 29487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028219</v>
       </c>
       <c r="B2" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127026790</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127027191</v>
       </c>
       <c r="B4" t="n">
-        <v>80118</v>
+        <v>80122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127028208</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127027248</v>
       </c>
       <c r="B6" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29487-2024 artfynd.xlsx
+++ b/artfynd/A 29487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028219</v>
       </c>
       <c r="B2" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127026790</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127027191</v>
       </c>
       <c r="B4" t="n">
-        <v>80122</v>
+        <v>80124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127028208</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127027248</v>
       </c>
       <c r="B6" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29487-2024 artfynd.xlsx
+++ b/artfynd/A 29487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028219</v>
       </c>
       <c r="B2" t="n">
-        <v>80124</v>
+        <v>80115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127026790</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127027191</v>
       </c>
       <c r="B4" t="n">
-        <v>80124</v>
+        <v>80115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>127028208</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127027248</v>
       </c>
       <c r="B6" t="n">
-        <v>75144</v>
+        <v>75135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29487-2024 artfynd.xlsx
+++ b/artfynd/A 29487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127028219</v>
+        <v>127027191</v>
       </c>
       <c r="B2" t="n">
-        <v>80124</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492886</v>
+        <v>492877</v>
       </c>
       <c r="R2" t="n">
-        <v>7143923</v>
+        <v>7143874</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127026790</v>
+        <v>127028219</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492866</v>
+        <v>492886</v>
       </c>
       <c r="R3" t="n">
-        <v>7143846</v>
+        <v>7143923</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127027191</v>
+        <v>127026790</v>
       </c>
       <c r="B4" t="n">
-        <v>80124</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492877</v>
+        <v>492866</v>
       </c>
       <c r="R4" t="n">
-        <v>7143874</v>
+        <v>7143846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127028208</v>
+        <v>127027248</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492886</v>
+        <v>492883</v>
       </c>
       <c r="R5" t="n">
-        <v>7143923</v>
+        <v>7143871</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127027248</v>
+        <v>127028208</v>
       </c>
       <c r="B6" t="n">
-        <v>75144</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492883</v>
+        <v>492886</v>
       </c>
       <c r="R6" t="n">
-        <v>7143871</v>
+        <v>7143923</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1182,111 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122743283</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gräningen Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>492867</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7143956</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29487-2024 artfynd.xlsx
+++ b/artfynd/A 29487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127027191</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028219</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127026790</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127027248</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028208</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,8 +1317,21 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122743283</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>